--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -999,17 +999,17 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Enterprise compliance platforms</t>
+          <t>Enterprise GRC platforms (OneTrust, IBM)</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>$50,000+/year</t>
+          <t>$50,000+/year (est.)</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Regula is free. Gap is real.</t>
+          <t>Regula is free. Gap is real. KLA Digital SaaS starts €299/mo.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="F10" s="26" t="inlineStr">
         <is>
-          <t>Listed on site (400K+ visitors)</t>
+          <t>Listed on site (150K+ users/mo)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>400K+ visitors/month</t>
+          <t>150K+ users/month (self-reported)</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 53 patterns, 11 frameworks, 8 languages. Generates Annex IV docs.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 53 patterns, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="H4" s="34" t="inlineStr">
         <is>
-          <t>Only tool with code-level depth + full CLI + CI/CD + doc generation. Free.</t>
+          <t>Most commands (33), most languages (8), only tool with Annex IV doc generation + evidence pack + gap scoring. Free.</t>
         </is>
       </c>
       <c r="I4" s="34" t="inlineStr">
         <is>
-          <t>Starting from 0. Late entrant.</t>
+          <t>Starting from 0. Late entrant. Systima overlaps on CLI+CI/CD.</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="H5" s="36" t="inlineStr">
         <is>
-          <t>No CLI, no CI/CD. Cannot integrate into a dev workflow. No code scanning.</t>
+          <t>No CLI, no CI/CD. Cannot integrate into a dev workflow. No codebase scanning.</t>
         </is>
       </c>
       <c r="I5" s="36" t="inlineStr">
@@ -3828,69 +3828,69 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
         <is>
-          <t>AgentGuard</t>
+          <t>Systima Comply</t>
         </is>
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>10 ★</t>
+          <t>0 ★</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
         <is>
-          <t>Runtime middleware</t>
+          <t>CLI / GitHub Action</t>
         </is>
       </c>
       <c r="D6" s="38" t="inlineStr">
         <is>
-          <t>3-line Python import. Wraps LLM agents. Runtime policy enforcement, not code scanning.</t>
-        </is>
-      </c>
-      <c r="E6" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="inlineStr">
-        <is>
-          <t>Yes (SDK)</t>
+          <t>npm package + GitHub Action + TypeScript API. Scans codebase for EU AI Act risks. Domain-based severity. PDF reports. Call-chain tracing.</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>Yes (GH Action)</t>
         </is>
       </c>
       <c r="G6" s="38" t="inlineStr">
         <is>
-          <t>Python (middleware)</t>
+          <t>JS/TS (npm)</t>
         </is>
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>Different use case: runtime vs scan-time. Complementary, not competitive.</t>
+          <t>Regula covers 8 languages vs JS/TS only. Regula has 33 commands and generates Annex IV docs; Systima focuses on scanning.</t>
         </is>
       </c>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>Could expand to code scanning, eating our niche</t>
+          <t>Direct competitor — CLI + CI/CD + codebase scanning. Created 14 Mar 2026.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>EU AI Radar</t>
+          <t>AgentGuard</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>10 ★</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Static web tool</t>
+          <t>Runtime middleware</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>5-question quiz. Maps to risk band. No code scanning.</t>
+          <t>3-line Python import. Wraps LLM agents. Runtime policy enforcement, not code scanning.</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
@@ -3898,140 +3898,140 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>Yes (SDK)</t>
         </is>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Python (middleware)</t>
         </is>
       </c>
       <c r="H7" s="36" t="inlineStr">
         <is>
-          <t>Trivial tool. Regula does what it does + 32 more commands.</t>
+          <t>Different use case: runtime vs scan-time. Complementary, not competitive.</t>
         </is>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
-          <t>Very low — different depth</t>
+          <t>Could expand to code scanning</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="38" t="inlineStr">
         <is>
-          <t>mcp-eu-ai-act</t>
+          <t>EU AI Radar</t>
         </is>
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>2 ★</t>
+          <t>?</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
-          <t>MCP server</t>
+          <t>Static web tool</t>
         </is>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>ArkForge MCP scanner. Detects EU AI Act violations via MCP protocol.</t>
-        </is>
-      </c>
-      <c r="E8" s="35" t="inlineStr">
-        <is>
-          <t>Via MCP</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr">
-        <is>
-          <t>Via MCP</t>
+          <t>5-question quiz. Maps to risk band. No code scanning.</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="G8" s="38" t="inlineStr">
         <is>
-          <t>MCP-compatible</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H8" s="38" t="inlineStr">
         <is>
-          <t>Very early. Our MCP server is a distribution channel, not a competitor.</t>
+          <t>Trivial tool. Different depth entirely.</t>
         </is>
       </c>
       <c r="I8" s="38" t="inlineStr">
         <is>
-          <t>Could gain traction with Claude/Cursor users before us</t>
+          <t>Very low — different depth</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>G0 (AgentBouncr)</t>
+          <t>mcp-eu-ai-act</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>2 ★</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>Agent control layer</t>
+          <t>MCP server</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>Scan, test, monitor for AI agents. LangChain/CrewAI/AutoGen/RAG. HMAC audit chains. ConsentGate.</t>
-        </is>
-      </c>
-      <c r="E9" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>ArkForge MCP scanner. Detects EU AI Act violations via MCP protocol.</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>Via MCP</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Via MCP</t>
         </is>
       </c>
       <c r="G9" s="36" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>MCP-compatible</t>
         </is>
       </c>
       <c r="H9" s="36" t="inlineStr">
         <is>
-          <t>Agent-focused vs code-focused. Different buyer.</t>
+          <t>Very early. Our MCP server is a distribution channel, not a competitor.</t>
         </is>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
-          <t>Could expand to code scanning</t>
+          <t>Could gain traction with Claude/Cursor users before us</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="38" t="inlineStr">
         <is>
-          <t>KLA Digital</t>
+          <t>G0 (AgentBouncr)</t>
         </is>
       </c>
       <c r="B10" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>?</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
-          <t>SaaS platform</t>
+          <t>Agent control layer</t>
         </is>
       </c>
       <c r="D10" s="38" t="inlineStr">
         <is>
-          <t>AI governance SaaS. Cross-framework mapping. €299+/month.</t>
+          <t>Scan, test, monitor for AI agents. LangChain/CrewAI/AutoGen/RAG. HMAC audit chains. ConsentGate.</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
@@ -4039,69 +4039,116 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="38" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="H10" s="38" t="inlineStr">
         <is>
-          <t>We're free. They target enterprise compliance officers, not developers.</t>
+          <t>Agent-focused vs code-focused. Different buyer.</t>
         </is>
       </c>
       <c r="I10" s="38" t="inlineStr">
         <is>
-          <t>Credibility: established brand vs unknown</t>
+          <t>Could expand to code scanning</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
+          <t>KLA Digital</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>SaaS platform</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>AI governance SaaS. Cross-framework mapping. €299+/month.</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>We're free. They target enterprise compliance officers, not developers.</t>
+        </is>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Credibility: established brand vs unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
           <t>OneTrust/Credo AI</t>
         </is>
       </c>
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Enterprise GRC</t>
         </is>
       </c>
-      <c r="D11" s="36" t="inlineStr">
-        <is>
-          <t>$50K+/year. Risk management, documentation, lifecycle.</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>Est. $50K+/year for enterprise contracts. Risk management, documentation, lifecycle.</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F11" s="37" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G11" s="36" t="inlineStr">
+      <c r="G12" s="38" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="H11" s="36" t="inlineStr">
+      <c r="H12" s="38" t="inlineStr">
         <is>
           <t>We're free. Entirely different buyer. Not a real competitor at our stage.</t>
         </is>
       </c>
-      <c r="I11" s="36" t="inlineStr">
+      <c r="I12" s="38" t="inlineStr">
         <is>
           <t>Credibility comparison if enterprise asks why not use them</t>
         </is>
@@ -4118,8 +4165,8 @@
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="39" t="inlineStr">
         <is>
-          <t>Regula has the deepest feature set in the open-source space (33 commands vs competitors' 1-5). The differentiation is real: code-level scanning + CLI + CI/CD + multi-language + doc generation in one free tool. No other open-source tool does all of this.
-The honest risk: EuConform has 107 stars and 4 months head start. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week EuConform compounds its lead.
+          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, Annex IV doc generation). One direct competitor on CLI + CI/CD exists: Systima Comply (npm/GitHub Action, JS/TS only, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is language breadth (8 vs 2) and depth (33 commands vs a scanner). EuConform leads on OSS mindshare (107 stars).
+The honest risk: EuConform has 107 stars and 4 months head start. Systima is a newer but direct competitor. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>
       </c>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -14,7 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 · OKR Tracker" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 · First 8 Weeks" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · 12-Month Roadmap'!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Distribution Channels'!$A$2:$H$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -416,6 +419,72 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="001B5E20"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00E65100"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF9C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00B71C1C"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCDD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <color rgb="00757575"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F5F5F5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <b val="1"/>
+        <color rgb="00F57F17"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF9C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -988,7 +1057,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Digital Omnibus may extend to Dec 2027 — treat Aug as binding</t>
+          <t>Digital Omnibus Council backstop: 2 Dec 2027 — trilogues ongoing. Treat Aug 2026 as working deadline until final text adopted.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -1004,12 +1073,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>$50,000+/year (est.)</t>
+          <t>No published list prices</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Regula is free. Gap is real. KLA Digital SaaS starts €299/mo.</t>
+          <t>Regula is free. OneTrust/IBM do not disclose AI governance pricing; analyst reports cite annual contracts well above €10,000.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
@@ -1030,7 +1099,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Regula eliminates the triage phase</t>
+          <t>Source: Intellera Consulting (2024). Covers compliance + conformity assessment per high-risk AI system. Regula eliminates the triage phase.</t>
         </is>
       </c>
       <c r="D17" s="2" t="n"/>
@@ -1041,7 +1110,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Max penalty</t>
+          <t>Max penalty (prohibited AI, Art.5)</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1051,7 +1120,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Exceeds GDPR — real compliance urgency</t>
+          <t>For prohibited practices only. High-risk AI non-compliance (Art.99): €15M or 3% turnover. Most SMEs face the lower tier.</t>
         </is>
       </c>
       <c r="D18" s="2" t="n"/>
@@ -1067,12 +1136,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>EuConform — 107 stars (Dec 2025)</t>
+          <t>EuConform — 107 ★ (Apr 2026)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Browser-based, no CLI, no CI/CD integration</t>
+          <t>Browser-based, no CLI, no CI/CD integration. Verified via GitHub API, April 2026.</t>
         </is>
       </c>
       <c r="D19" s="2" t="n"/>
@@ -1930,6 +1999,25 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:G9"/>
   </mergeCells>
+  <conditionalFormatting sqref="G26:G40">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Not started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G26:G40" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"Not started,In progress,Done,Blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1964,7 +2052,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Key external date: EU AI Act Annex III enforcement — 2 August 2026</t>
+          <t>Working deadline: EU AI Act Annex III — 2 Aug 2026 (Digital Omnibus backstop: 2 Dec 2027, trilogues ongoing)</t>
         </is>
       </c>
     </row>
@@ -2977,10 +3065,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:I3"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
+  <conditionalFormatting sqref="G4:G25">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Not started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="G4:G25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"Not started,In progress,Done,Blocked"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H4:H25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3642,9 +3753,32 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:H2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H3:H20">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"In progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Blocked"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Not started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="H3:H20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"Not started,In progress,Done,Blocked"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A3:A20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3786,7 +3920,8 @@
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>107 ★</t>
+          <t>107 ★
+(Apr 2026)</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -3821,7 +3956,7 @@
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
-          <t>107 stars vs 0 — strong first-mover advantage in OSS space</t>
+          <t>107 stars as of Apr 2026 — strong first-mover advantage in OSS space</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4213,7 @@
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>AI governance SaaS. Cross-framework mapping. €299+/month.</t>
+          <t>AI governance SaaS. Cross-framework mapping. Pricing on request — no public list prices (Apr 2026).</t>
         </is>
       </c>
       <c r="E11" s="37" t="inlineStr">
@@ -4188,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4413,6 +4548,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
@@ -4618,6 +4754,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
@@ -4823,6 +4960,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -5028,6 +5166,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
@@ -5070,6 +5209,41 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A12:H12"/>
@@ -5084,6 +5258,22 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
+  <conditionalFormatting sqref="H4:H80">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"G"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="H4:H80" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"G,A,R"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5444,6 +5634,19 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <conditionalFormatting sqref="E4:E12">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Done"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
+      <formula>"Skipped"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E4:E12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid entry" error="Choose a value from the dropdown." type="list">
+      <formula1>"Done,Not done,Skipped"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -237,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -264,11 +264,55 @@
         <color rgb="00DEE2E6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DEE2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DEE2E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DEE2E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DEE2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DEE2E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DEE2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DEE2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -382,6 +426,11 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1057,7 +1106,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Digital Omnibus Council backstop: 2 Dec 2027 — trilogues ongoing. Treat Aug 2026 as working deadline until final text adopted.</t>
+          <t>Digital Omnibus backstops: 2 Dec 2027 (stand-alone high-risk) / 2 Aug 2028 (embedded in products) — trilogues ongoing. Treat Aug 2026 as working deadline.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
@@ -2052,7 +2101,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Working deadline: EU AI Act Annex III — 2 Aug 2026 (Digital Omnibus backstop: 2 Dec 2027, trilogues ongoing)</t>
+          <t>Working deadline: 2 Aug 2026 · Omnibus backstops: 2 Dec 2027 (stand-alone) / 2 Aug 2028 (embedded) — trilogues ongoing</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3231,7 @@
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
-          <t>50K–500K impressions if front page</t>
+          <t>~10K–100K unique visits if front page (reported outcomes)</t>
         </is>
       </c>
       <c r="E3" s="27" t="inlineStr">
@@ -3883,7 +3932,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 53 patterns, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 49 patterns, 12 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">
@@ -3993,12 +4042,12 @@
       </c>
       <c r="G6" s="38" t="inlineStr">
         <is>
-          <t>JS/TS (npm)</t>
+          <t>TS-native; also scans Py/Go/Java/Rust via tree-sitter</t>
         </is>
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>Regula covers 8 languages vs JS/TS only. Regula has 33 commands and generates Annex IV docs; Systima focuses on scanning.</t>
+          <t>Regula covers 8 languages with dedicated patterns; Systima is TypeScript-native. Regula has 33 commands and generates Annex IV docs.</t>
         </is>
       </c>
       <c r="I6" s="38" t="inlineStr">
@@ -4245,7 +4294,7 @@
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="38" t="inlineStr">
         <is>
-          <t>OneTrust/Credo AI</t>
+          <t>EuroComply</t>
         </is>
       </c>
       <c r="B12" s="38" t="inlineStr">
@@ -4255,12 +4304,12 @@
       </c>
       <c r="C12" s="38" t="inlineStr">
         <is>
-          <t>Enterprise GRC</t>
+          <t>SaaS — SME-focused</t>
         </is>
       </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
-          <t>Est. $50K+/year for enterprise contracts. Risk management, documentation, lifecycle.</t>
+          <t>EU AI Act + NIS2 + GDPR + CRA + Data Act in one platform. Browser-based.</t>
         </is>
       </c>
       <c r="E12" s="37" t="inlineStr">
@@ -4280,31 +4329,93 @@
       </c>
       <c r="H12" s="38" t="inlineStr">
         <is>
-          <t>We're free. Entirely different buyer. Not a real competitor at our stage.</t>
+          <t>Targets same SME audience. Broader regulation coverage. No code scanning.</t>
         </is>
       </c>
       <c r="I12" s="38" t="inlineStr">
         <is>
-          <t>Credibility comparison if enterprise asks why not use them</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="10" customHeight="1"/>
+          <t>Most direct SaaS overlap with Regula's audience</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="10" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>compl-ai</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>OSS eval framework</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Open-source compliance-centred evaluation for generative AI. compl-ai.org. Research-grade.</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>Research-focused, not developer-focused. Different use case.</t>
+        </is>
+      </c>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Could grow into developer tool territory</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>HONEST ASSESSMENT</t>
         </is>
       </c>
+      <c r="B14" s="40" t="n"/>
+      <c r="C14" s="40" t="n"/>
+      <c r="D14" s="40" t="n"/>
+      <c r="E14" s="40" t="n"/>
+      <c r="F14" s="40" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="40" t="n"/>
+      <c r="I14" s="41" t="n"/>
     </row>
     <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, Annex IV doc generation). One direct competitor on CLI + CI/CD exists: Systima Comply (npm/GitHub Action, JS/TS only, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is language breadth (8 vs 2) and depth (33 commands vs a scanner). EuConform leads on OSS mindshare (107 stars).
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 12 frameworks, 49 patterns, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (49 dedicated patterns vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
 The honest risk: EuConform has 107 stars and 4 months head start. Systima is a newer but direct competitor. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>
       </c>
+      <c r="B15" s="40" t="n"/>
+      <c r="C15" s="40" t="n"/>
+      <c r="D15" s="40" t="n"/>
+      <c r="E15" s="40" t="n"/>
+      <c r="F15" s="40" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="40" t="n"/>
+      <c r="I15" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4393,156 +4504,156 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="40" t="inlineStr"/>
-      <c r="E5" s="40" t="inlineStr"/>
-      <c r="F5" s="40" t="inlineStr"/>
-      <c r="G5" s="40" t="inlineStr"/>
-      <c r="H5" s="41" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr"/>
+      <c r="E5" s="43" t="inlineStr"/>
+      <c r="F5" s="43" t="inlineStr"/>
+      <c r="G5" s="43" t="inlineStr"/>
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>PyPI downloads (total)</t>
         </is>
       </c>
-      <c r="B6" s="42" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C6" s="42" t="inlineStr">
+      <c r="C6" s="45" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D6" s="42" t="inlineStr"/>
-      <c r="E6" s="42" t="inlineStr"/>
-      <c r="F6" s="42" t="inlineStr"/>
-      <c r="G6" s="42" t="inlineStr"/>
-      <c r="H6" s="41" t="inlineStr">
+      <c r="D6" s="45" t="inlineStr"/>
+      <c r="E6" s="45" t="inlineStr"/>
+      <c r="F6" s="45" t="inlineStr"/>
+      <c r="G6" s="45" t="inlineStr"/>
+      <c r="H6" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>Show HN submitted</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr"/>
-      <c r="E7" s="40" t="inlineStr"/>
-      <c r="F7" s="40" t="inlineStr"/>
-      <c r="G7" s="40" t="inlineStr"/>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="D7" s="43" t="inlineStr"/>
+      <c r="E7" s="43" t="inlineStr"/>
+      <c r="F7" s="43" t="inlineStr"/>
+      <c r="G7" s="43" t="inlineStr"/>
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>DEV.to article published</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C8" s="42" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D8" s="42" t="inlineStr"/>
-      <c r="E8" s="42" t="inlineStr"/>
-      <c r="F8" s="42" t="inlineStr"/>
-      <c r="G8" s="42" t="inlineStr"/>
-      <c r="H8" s="41" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr"/>
+      <c r="E8" s="45" t="inlineStr"/>
+      <c r="F8" s="45" t="inlineStr"/>
+      <c r="G8" s="45" t="inlineStr"/>
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>Landing page verified live</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr"/>
-      <c r="E9" s="40" t="inlineStr"/>
-      <c r="F9" s="40" t="inlineStr"/>
-      <c r="G9" s="40" t="inlineStr"/>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="D9" s="43" t="inlineStr"/>
+      <c r="E9" s="43" t="inlineStr"/>
+      <c r="F9" s="43" t="inlineStr"/>
+      <c r="G9" s="43" t="inlineStr"/>
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>awesome-claude-code PR</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="42" t="inlineStr"/>
-      <c r="E10" s="42" t="inlineStr"/>
-      <c r="F10" s="42" t="inlineStr"/>
-      <c r="G10" s="42" t="inlineStr"/>
-      <c r="H10" s="41" t="inlineStr">
+      <c r="D10" s="45" t="inlineStr"/>
+      <c r="E10" s="45" t="inlineStr"/>
+      <c r="F10" s="45" t="inlineStr"/>
+      <c r="G10" s="45" t="inlineStr"/>
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -4550,7 +4661,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>Q2 Jul–Sep 2026  ·  Theme: Ecosystem &amp; deadline window</t>
         </is>
@@ -4599,156 +4710,156 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="45" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C14" s="42" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="42" t="inlineStr"/>
-      <c r="E14" s="42" t="inlineStr"/>
-      <c r="F14" s="42" t="inlineStr"/>
-      <c r="G14" s="42" t="inlineStr"/>
-      <c r="H14" s="41" t="inlineStr">
+      <c r="D14" s="45" t="inlineStr"/>
+      <c r="E14" s="45" t="inlineStr"/>
+      <c r="F14" s="45" t="inlineStr"/>
+      <c r="G14" s="45" t="inlineStr"/>
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D15" s="40" t="inlineStr"/>
-      <c r="E15" s="40" t="inlineStr"/>
-      <c r="F15" s="40" t="inlineStr"/>
-      <c r="G15" s="40" t="inlineStr"/>
-      <c r="H15" s="41" t="inlineStr">
+      <c r="D15" s="43" t="inlineStr"/>
+      <c r="E15" s="43" t="inlineStr"/>
+      <c r="F15" s="43" t="inlineStr"/>
+      <c r="G15" s="43" t="inlineStr"/>
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="42" t="inlineStr">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t>artificialintelligenceact.eu listed</t>
         </is>
       </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C16" s="42" t="inlineStr">
+      <c r="C16" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D16" s="42" t="inlineStr"/>
-      <c r="E16" s="42" t="inlineStr"/>
-      <c r="F16" s="42" t="inlineStr"/>
-      <c r="G16" s="42" t="inlineStr"/>
-      <c r="H16" s="41" t="inlineStr">
+      <c r="D16" s="45" t="inlineStr"/>
+      <c r="E16" s="45" t="inlineStr"/>
+      <c r="F16" s="45" t="inlineStr"/>
+      <c r="G16" s="45" t="inlineStr"/>
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>LinkedIn posts published</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr"/>
-      <c r="E17" s="40" t="inlineStr"/>
-      <c r="F17" s="40" t="inlineStr"/>
-      <c r="G17" s="40" t="inlineStr"/>
-      <c r="H17" s="41" t="inlineStr">
+      <c r="D17" s="43" t="inlineStr"/>
+      <c r="E17" s="43" t="inlineStr"/>
+      <c r="F17" s="43" t="inlineStr"/>
+      <c r="G17" s="43" t="inlineStr"/>
+      <c r="H17" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="42" t="inlineStr">
+      <c r="A18" s="45" t="inlineStr">
         <is>
           <t>Real-world eval published</t>
         </is>
       </c>
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D18" s="42" t="inlineStr"/>
-      <c r="E18" s="42" t="inlineStr"/>
-      <c r="F18" s="42" t="inlineStr"/>
-      <c r="G18" s="42" t="inlineStr"/>
-      <c r="H18" s="41" t="inlineStr">
+      <c r="D18" s="45" t="inlineStr"/>
+      <c r="E18" s="45" t="inlineStr"/>
+      <c r="F18" s="45" t="inlineStr"/>
+      <c r="G18" s="45" t="inlineStr"/>
+      <c r="H18" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>Aug 2 blog post live</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr"/>
-      <c r="E19" s="40" t="inlineStr"/>
-      <c r="F19" s="40" t="inlineStr"/>
-      <c r="G19" s="40" t="inlineStr"/>
-      <c r="H19" s="41" t="inlineStr">
+      <c r="D19" s="43" t="inlineStr"/>
+      <c r="E19" s="43" t="inlineStr"/>
+      <c r="F19" s="43" t="inlineStr"/>
+      <c r="G19" s="43" t="inlineStr"/>
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -4756,7 +4867,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="47" t="inlineStr">
         <is>
           <t>Q3 Oct–Dec 2026  ·  Theme: Growth &amp; community</t>
         </is>
@@ -4805,156 +4916,156 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C23" s="40" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D23" s="40" t="inlineStr"/>
-      <c r="E23" s="40" t="inlineStr"/>
-      <c r="F23" s="40" t="inlineStr"/>
-      <c r="G23" s="40" t="inlineStr"/>
-      <c r="H23" s="41" t="inlineStr">
+      <c r="D23" s="43" t="inlineStr"/>
+      <c r="E23" s="43" t="inlineStr"/>
+      <c r="F23" s="43" t="inlineStr"/>
+      <c r="G23" s="43" t="inlineStr"/>
+      <c r="H23" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B24" s="42" t="inlineStr">
+      <c r="B24" s="45" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="45" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="D24" s="42" t="inlineStr"/>
-      <c r="E24" s="42" t="inlineStr"/>
-      <c r="F24" s="42" t="inlineStr"/>
-      <c r="G24" s="42" t="inlineStr"/>
-      <c r="H24" s="41" t="inlineStr">
+      <c r="D24" s="45" t="inlineStr"/>
+      <c r="E24" s="45" t="inlineStr"/>
+      <c r="F24" s="45" t="inlineStr"/>
+      <c r="G24" s="45" t="inlineStr"/>
+      <c r="H24" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>User-filed GitHub issues</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="40" t="inlineStr"/>
-      <c r="E25" s="40" t="inlineStr"/>
-      <c r="F25" s="40" t="inlineStr"/>
-      <c r="G25" s="40" t="inlineStr"/>
-      <c r="H25" s="41" t="inlineStr">
+      <c r="D25" s="43" t="inlineStr"/>
+      <c r="E25" s="43" t="inlineStr"/>
+      <c r="F25" s="43" t="inlineStr"/>
+      <c r="G25" s="43" t="inlineStr"/>
+      <c r="H25" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
+      <c r="A26" s="45" t="inlineStr">
         <is>
           <t>v1.6.0 shipped</t>
         </is>
       </c>
-      <c r="B26" s="42" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D26" s="42" t="inlineStr"/>
-      <c r="E26" s="42" t="inlineStr"/>
-      <c r="F26" s="42" t="inlineStr"/>
-      <c r="G26" s="42" t="inlineStr"/>
-      <c r="H26" s="41" t="inlineStr">
+      <c r="D26" s="45" t="inlineStr"/>
+      <c r="E26" s="45" t="inlineStr"/>
+      <c r="F26" s="45" t="inlineStr"/>
+      <c r="G26" s="45" t="inlineStr"/>
+      <c r="H26" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>r/python post submitted</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D27" s="40" t="inlineStr"/>
-      <c r="E27" s="40" t="inlineStr"/>
-      <c r="F27" s="40" t="inlineStr"/>
-      <c r="G27" s="40" t="inlineStr"/>
-      <c r="H27" s="41" t="inlineStr">
+      <c r="D27" s="43" t="inlineStr"/>
+      <c r="E27" s="43" t="inlineStr"/>
+      <c r="F27" s="43" t="inlineStr"/>
+      <c r="G27" s="43" t="inlineStr"/>
+      <c r="H27" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="A28" s="45" t="inlineStr">
         <is>
           <t>False positive rate (OSS)</t>
         </is>
       </c>
-      <c r="B28" s="42" t="inlineStr">
+      <c r="B28" s="45" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C28" s="42" t="inlineStr">
+      <c r="C28" s="45" t="inlineStr">
         <is>
           <t>&lt; 5%</t>
         </is>
       </c>
-      <c r="D28" s="42" t="inlineStr"/>
-      <c r="E28" s="42" t="inlineStr"/>
-      <c r="F28" s="42" t="inlineStr"/>
-      <c r="G28" s="42" t="inlineStr"/>
-      <c r="H28" s="41" t="inlineStr">
+      <c r="D28" s="45" t="inlineStr"/>
+      <c r="E28" s="45" t="inlineStr"/>
+      <c r="F28" s="45" t="inlineStr"/>
+      <c r="G28" s="45" t="inlineStr"/>
+      <c r="H28" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -5011,156 +5122,156 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="A32" s="45" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B32" s="42" t="inlineStr">
+      <c r="B32" s="45" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C32" s="42" t="inlineStr">
+      <c r="C32" s="45" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D32" s="42" t="inlineStr"/>
-      <c r="E32" s="42" t="inlineStr"/>
-      <c r="F32" s="42" t="inlineStr"/>
-      <c r="G32" s="42" t="inlineStr"/>
-      <c r="H32" s="41" t="inlineStr">
+      <c r="D32" s="45" t="inlineStr"/>
+      <c r="E32" s="45" t="inlineStr"/>
+      <c r="F32" s="45" t="inlineStr"/>
+      <c r="G32" s="45" t="inlineStr"/>
+      <c r="H32" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="43" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr"/>
-      <c r="E33" s="40" t="inlineStr"/>
-      <c r="F33" s="40" t="inlineStr"/>
-      <c r="G33" s="40" t="inlineStr"/>
-      <c r="H33" s="41" t="inlineStr">
+      <c r="D33" s="43" t="inlineStr"/>
+      <c r="E33" s="43" t="inlineStr"/>
+      <c r="F33" s="43" t="inlineStr"/>
+      <c r="G33" s="43" t="inlineStr"/>
+      <c r="H33" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>GitHub Sponsors live</t>
         </is>
       </c>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B34" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C34" s="42" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D34" s="42" t="inlineStr"/>
-      <c r="E34" s="42" t="inlineStr"/>
-      <c r="F34" s="42" t="inlineStr"/>
-      <c r="G34" s="42" t="inlineStr"/>
-      <c r="H34" s="41" t="inlineStr">
+      <c r="D34" s="45" t="inlineStr"/>
+      <c r="E34" s="45" t="inlineStr"/>
+      <c r="F34" s="45" t="inlineStr"/>
+      <c r="G34" s="45" t="inlineStr"/>
+      <c r="H34" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="40" t="inlineStr">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>Enterprise enquiries</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D35" s="40" t="inlineStr"/>
-      <c r="E35" s="40" t="inlineStr"/>
-      <c r="F35" s="40" t="inlineStr"/>
-      <c r="G35" s="40" t="inlineStr"/>
-      <c r="H35" s="41" t="inlineStr">
+      <c r="D35" s="43" t="inlineStr"/>
+      <c r="E35" s="43" t="inlineStr"/>
+      <c r="F35" s="43" t="inlineStr"/>
+      <c r="G35" s="43" t="inlineStr"/>
+      <c r="H35" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="45" t="inlineStr">
         <is>
           <t>Year-1 retro published</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C36" s="45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D36" s="42" t="inlineStr"/>
-      <c r="E36" s="42" t="inlineStr"/>
-      <c r="F36" s="42" t="inlineStr"/>
-      <c r="G36" s="42" t="inlineStr"/>
-      <c r="H36" s="41" t="inlineStr">
+      <c r="D36" s="45" t="inlineStr"/>
+      <c r="E36" s="45" t="inlineStr"/>
+      <c r="F36" s="45" t="inlineStr"/>
+      <c r="G36" s="45" t="inlineStr"/>
+      <c r="H36" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="40" t="inlineStr">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>v2.0 roadmap defined</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C37" s="40" t="inlineStr">
+      <c r="C37" s="43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D37" s="40" t="inlineStr"/>
-      <c r="E37" s="40" t="inlineStr"/>
-      <c r="F37" s="40" t="inlineStr"/>
-      <c r="G37" s="40" t="inlineStr"/>
-      <c r="H37" s="41" t="inlineStr">
+      <c r="D37" s="43" t="inlineStr"/>
+      <c r="E37" s="43" t="inlineStr"/>
+      <c r="F37" s="43" t="inlineStr"/>
+      <c r="G37" s="43" t="inlineStr"/>
+      <c r="H37" s="44" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -5175,35 +5286,35 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="45" t="inlineStr">
+      <c r="A40" s="48" t="inlineStr">
         <is>
           <t>• Update the Week columns each Friday. Enter actual numbers, not estimates.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="45" t="inlineStr">
+      <c r="A41" s="48" t="inlineStr">
         <is>
           <t>• RAG = Red (off track, needs action) / Amber (at risk, monitor) / Green (on track).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="45" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>• A metric that stays Red for 2+ weeks needs a plan change, not a colour change.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="45" t="inlineStr">
+      <c r="A43" s="48" t="inlineStr">
         <is>
           <t>• Baseline = value at start of quarter. Target = realistic stretch, based on market data above.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="45" t="inlineStr">
+      <c r="A44" s="48" t="inlineStr">
         <is>
           <t>• Do not update baselines mid-quarter — that hides regression.</t>
         </is>
@@ -5303,7 +5414,7 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="46" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>These 8 weeks determine whether the Show HN lands before or after the August deadline crowd</t>
         </is>
@@ -5342,7 +5453,7 @@
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="47" t="inlineStr">
+      <c r="A4" s="50" t="inlineStr">
         <is>
           <t>Wk 1</t>
         </is>
@@ -5352,7 +5463,7 @@
           <t>Apr 3–9</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
         <is>
           <t>Pre-launch: repo &amp; landing</t>
         </is>
@@ -5366,7 +5477,7 @@
 □ Verify PyPI page renders description correctly</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5378,7 +5489,7 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Wk 2</t>
         </is>
@@ -5388,7 +5499,7 @@
           <t>Apr 10–16</t>
         </is>
       </c>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>Pre-launch: DEV.to research</t>
         </is>
@@ -5402,7 +5513,7 @@
 □ Draft DEV.to article outline</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5414,7 +5525,7 @@
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="47" t="inlineStr">
+      <c r="A6" s="50" t="inlineStr">
         <is>
           <t>Wk 3</t>
         </is>
@@ -5424,7 +5535,7 @@
           <t>Apr 17–23</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="50" t="inlineStr">
         <is>
           <t>DEV.to article: write &amp; publish</t>
         </is>
@@ -5438,7 +5549,7 @@
 □ Share on LinkedIn</t>
         </is>
       </c>
-      <c r="E6" s="48" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5450,7 +5561,7 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Wk 4</t>
         </is>
@@ -5460,7 +5571,7 @@
           <t>Apr 24–30</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>Show HN prep</t>
         </is>
@@ -5474,7 +5585,7 @@
 □ Block 4 hours in calendar for that day</t>
         </is>
       </c>
-      <c r="E7" s="48" t="inlineStr">
+      <c r="E7" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5486,7 +5597,7 @@
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>Wk 5</t>
         </is>
@@ -5496,7 +5607,7 @@
           <t>May 1–7</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Show HN LAUNCH</t>
         </is>
@@ -5510,7 +5621,7 @@
 □ Thank people who try it and report results</t>
         </is>
       </c>
-      <c r="E8" s="48" t="inlineStr">
+      <c r="E8" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5522,7 +5633,7 @@
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="49" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>Wk 6</t>
         </is>
@@ -5532,7 +5643,7 @@
           <t>May 8–14</t>
         </is>
       </c>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="52" t="inlineStr">
         <is>
           <t>Post-HN: follow-up &amp; ecosystem</t>
         </is>
@@ -5546,7 +5657,7 @@
 □ Note which questions came up most — update FAQ</t>
         </is>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5558,7 +5669,7 @@
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>Wk 7</t>
         </is>
@@ -5568,7 +5679,7 @@
           <t>May 15–21</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
         <is>
           <t>Product Hunt prep</t>
         </is>
@@ -5582,7 +5693,7 @@
 □ Schedule for Tuesday launch</t>
         </is>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5594,7 +5705,7 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="49" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>Wk 8</t>
         </is>
@@ -5604,7 +5715,7 @@
           <t>May 22–29</t>
         </is>
       </c>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="52" t="inlineStr">
         <is>
           <t>EU ecosystem outreach begins</t>
         </is>
@@ -5618,7 +5729,7 @@
 □ Review GitHub stars — assess HN impact honestly</t>
         </is>
       </c>
-      <c r="E11" s="48" t="inlineStr">
+      <c r="E11" s="51" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 49 patterns, 12 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 49 patterns, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 49 patterns, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 32 named pattern groups, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 12 frameworks, 49 patterns, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (49 dedicated patterns vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
+          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, 32 named pattern groups, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (32 named groups vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
 The honest risk: EuConform has 107 stars and 4 months head start. Systima is a newer but direct competitor. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -3932,7 +3932,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 32 named pattern groups, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 36 named pattern groups, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, 32 named pattern groups, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (32 named groups vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
+          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (32 named groups vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
 The honest risk: EuConform has 107 stars and 4 months head start. Systima is a newer but direct competitor. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -237,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -264,55 +264,11 @@
         <color rgb="00DEE2E6"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DEE2E6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DEE2E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DEE2E6"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DEE2E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DEE2E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DEE2E6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DEE2E6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DEE2E6"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -426,11 +382,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3838,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3952,7 +3903,7 @@
       </c>
       <c r="H4" s="34" t="inlineStr">
         <is>
-          <t>Most commands (33), most languages (8), only tool with Annex IV doc generation + evidence pack + gap scoring. Free.</t>
+          <t>Most commands (33), most languages (8), deepest pattern coverage (36 named groups); Annex IV + evidence pack + gap scoring + remediation plan in one free tool.</t>
         </is>
       </c>
       <c r="I4" s="34" t="inlineStr">
@@ -4027,7 +3978,7 @@
       </c>
       <c r="D6" s="38" t="inlineStr">
         <is>
-          <t>npm package + GitHub Action + TypeScript API. Scans codebase for EU AI Act risks. Domain-based severity. PDF reports. Call-chain tracing.</t>
+          <t>npm package + GitHub Action + TypeScript API. Scans codebase for EU AI Act risks. Domain-based severity. PDF reports. Call-chain tracing. 37+ AI frameworks via tree-sitter WASM.</t>
         </is>
       </c>
       <c r="E6" s="35" t="inlineStr">
@@ -4047,12 +3998,12 @@
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>Regula covers 8 languages with dedicated patterns; Systima is TypeScript-native. Regula has 33 commands and generates Annex IV docs.</t>
+          <t>Regula: 33 commands vs Systima's scan-only; dedicated per-language patterns (36 named groups); evidence pack, gap scoring, and remediation plan. Both generate compliance docs.</t>
         </is>
       </c>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>Direct competitor — CLI + CI/CD + codebase scanning. Created 14 Mar 2026.</t>
+          <t>Direct competitor — CLI + CI/CD + codebase scanning. Org created 6 Mar 2026.</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="10" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
           <t>compl-ai</t>
@@ -4385,44 +4336,172 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="39" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>Microsoft Agent
+Governance Toolkit</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>Enterprise toolkit</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>Policy enforcement, zero-trust identity, sandboxing for AI agents. Published 2 Apr 2026.</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="inlineStr">
+        <is>
+          <t>Via SDK</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="38" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>Enterprise-only. Microsoft ecosystem. Not code scanning.</t>
+        </is>
+      </c>
+      <c r="I14" s="38" t="inlineStr">
+        <is>
+          <t>High credibility. Developer mindshare risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>OneTrust/Credo AI</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Enterprise GRC</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="inlineStr">
+        <is>
+          <t>Est. $50K+/year for enterprise contracts. Risk management, documentation, lifecycle.</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>We're free. Entirely different buyer. Not a real competitor at our stage.</t>
+        </is>
+      </c>
+      <c r="I15" s="36" t="inlineStr">
+        <is>
+          <t>Credibility comparison if enterprise asks why not use them</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>ARQNXS/eu-ai-act
+-compliance-checker</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>CLI / script</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>Python script. Scans codebases for EU AI Act compliance. GitHub repo (ARQNXS/eu-ai-act-compliance-checker).</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="38" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="H16" s="38" t="inlineStr">
+        <is>
+          <t>Very early stage. No CI/CD integration, no framework mapping, no doc generation.</t>
+        </is>
+      </c>
+      <c r="I16" s="38" t="inlineStr">
+        <is>
+          <t>Low — different depth. Found Apr 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="10" customHeight="1"/>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>HONEST ASSESSMENT</t>
         </is>
       </c>
-      <c r="B14" s="40" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="40" t="n"/>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="40" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="40" t="n"/>
-      <c r="I14" s="41" t="n"/>
-    </row>
-    <row r="15" ht="70" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>Regula has the broadest feature set in the open-source space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation). One direct CLI+CI/CD competitor exists: Systima Comply (TypeScript-native, also scans Py/Go/Java/Rust via tree-sitter, created 14 Mar 2026, 0 stars). Regula's advantage over Systima is pattern depth (32 named groups vs scanner heuristics) and command breadth (33 commands vs scan-only). EuConform leads on OSS mindshare (107 stars, Apr 2026).
-The honest risk: EuConform has 107 stars and 4 months head start. Systima is a newer but direct competitor. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Regula has the broadest feature set in the open-source CLI space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation, evidence pack, gap scoring, remediation plan). Two direct CLI+CI/CD competitors: Systima Comply (TS-native + tree-sitter, 37+ frameworks, PDF reports, org created 6 Mar 2026, 0 stars) and ARQNXS/eu-ai-act-compliance-checker (Python script, early stage). Regula's advantage over Systima: 33 commands vs scan-only; 36 named pattern groups with dedicated per-language depth; SBOM, inventory, bias eval, and Annex IV docs in one tool. Both tools generate compliance documentation. EuConform leads on OSS mindshare (107 ★ as of Apr 2026 — browser-only, no CLI, no CI/CD).
+The honest risk: EuConform has 107 stars and 4 months head start. Systima is a direct technical competitor with CLI + CI/CD + compliance doc generation. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>
       </c>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="40" t="n"/>
-      <c r="G15" s="40" t="n"/>
-      <c r="H15" s="40" t="n"/>
-      <c r="I15" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A15:I15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4504,156 +4583,156 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr"/>
-      <c r="E5" s="43" t="inlineStr"/>
-      <c r="F5" s="43" t="inlineStr"/>
-      <c r="G5" s="43" t="inlineStr"/>
-      <c r="H5" s="44" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr"/>
+      <c r="E5" s="40" t="inlineStr"/>
+      <c r="F5" s="40" t="inlineStr"/>
+      <c r="G5" s="40" t="inlineStr"/>
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="45" t="inlineStr">
+      <c r="A6" s="42" t="inlineStr">
         <is>
           <t>PyPI downloads (total)</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C6" s="45" t="inlineStr">
+      <c r="C6" s="42" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D6" s="45" t="inlineStr"/>
-      <c r="E6" s="45" t="inlineStr"/>
-      <c r="F6" s="45" t="inlineStr"/>
-      <c r="G6" s="45" t="inlineStr"/>
-      <c r="H6" s="44" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr"/>
+      <c r="E6" s="42" t="inlineStr"/>
+      <c r="F6" s="42" t="inlineStr"/>
+      <c r="G6" s="42" t="inlineStr"/>
+      <c r="H6" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
         <is>
           <t>Show HN submitted</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr"/>
-      <c r="E7" s="43" t="inlineStr"/>
-      <c r="F7" s="43" t="inlineStr"/>
-      <c r="G7" s="43" t="inlineStr"/>
-      <c r="H7" s="44" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr"/>
+      <c r="E7" s="40" t="inlineStr"/>
+      <c r="F7" s="40" t="inlineStr"/>
+      <c r="G7" s="40" t="inlineStr"/>
+      <c r="H7" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="42" t="inlineStr">
         <is>
           <t>DEV.to article published</t>
         </is>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr"/>
-      <c r="E8" s="45" t="inlineStr"/>
-      <c r="F8" s="45" t="inlineStr"/>
-      <c r="G8" s="45" t="inlineStr"/>
-      <c r="H8" s="44" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr"/>
+      <c r="E8" s="42" t="inlineStr"/>
+      <c r="F8" s="42" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr"/>
+      <c r="H8" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>Landing page verified live</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr"/>
-      <c r="E9" s="43" t="inlineStr"/>
-      <c r="F9" s="43" t="inlineStr"/>
-      <c r="G9" s="43" t="inlineStr"/>
-      <c r="H9" s="44" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr"/>
+      <c r="E9" s="40" t="inlineStr"/>
+      <c r="F9" s="40" t="inlineStr"/>
+      <c r="G9" s="40" t="inlineStr"/>
+      <c r="H9" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>awesome-claude-code PR</t>
         </is>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C10" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="45" t="inlineStr"/>
-      <c r="E10" s="45" t="inlineStr"/>
-      <c r="F10" s="45" t="inlineStr"/>
-      <c r="G10" s="45" t="inlineStr"/>
-      <c r="H10" s="44" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr"/>
+      <c r="E10" s="42" t="inlineStr"/>
+      <c r="F10" s="42" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr"/>
+      <c r="H10" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -4661,7 +4740,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="46" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>Q2 Jul–Sep 2026  ·  Theme: Ecosystem &amp; deadline window</t>
         </is>
@@ -4710,156 +4789,156 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C14" s="45" t="inlineStr">
+      <c r="C14" s="42" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="45" t="inlineStr"/>
-      <c r="E14" s="45" t="inlineStr"/>
-      <c r="F14" s="45" t="inlineStr"/>
-      <c r="G14" s="45" t="inlineStr"/>
-      <c r="H14" s="44" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr"/>
+      <c r="E14" s="42" t="inlineStr"/>
+      <c r="F14" s="42" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr"/>
+      <c r="H14" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr"/>
-      <c r="E15" s="43" t="inlineStr"/>
-      <c r="F15" s="43" t="inlineStr"/>
-      <c r="G15" s="43" t="inlineStr"/>
-      <c r="H15" s="44" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr"/>
+      <c r="E15" s="40" t="inlineStr"/>
+      <c r="F15" s="40" t="inlineStr"/>
+      <c r="G15" s="40" t="inlineStr"/>
+      <c r="H15" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="A16" s="42" t="inlineStr">
         <is>
           <t>artificialintelligenceact.eu listed</t>
         </is>
       </c>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C16" s="45" t="inlineStr">
+      <c r="C16" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D16" s="45" t="inlineStr"/>
-      <c r="E16" s="45" t="inlineStr"/>
-      <c r="F16" s="45" t="inlineStr"/>
-      <c r="G16" s="45" t="inlineStr"/>
-      <c r="H16" s="44" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr"/>
+      <c r="E16" s="42" t="inlineStr"/>
+      <c r="F16" s="42" t="inlineStr"/>
+      <c r="G16" s="42" t="inlineStr"/>
+      <c r="H16" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>LinkedIn posts published</t>
         </is>
       </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr"/>
-      <c r="E17" s="43" t="inlineStr"/>
-      <c r="F17" s="43" t="inlineStr"/>
-      <c r="G17" s="43" t="inlineStr"/>
-      <c r="H17" s="44" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr"/>
+      <c r="E17" s="40" t="inlineStr"/>
+      <c r="F17" s="40" t="inlineStr"/>
+      <c r="G17" s="40" t="inlineStr"/>
+      <c r="H17" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="42" t="inlineStr">
         <is>
           <t>Real-world eval published</t>
         </is>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C18" s="45" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr"/>
-      <c r="E18" s="45" t="inlineStr"/>
-      <c r="F18" s="45" t="inlineStr"/>
-      <c r="G18" s="45" t="inlineStr"/>
-      <c r="H18" s="44" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr"/>
+      <c r="E18" s="42" t="inlineStr"/>
+      <c r="F18" s="42" t="inlineStr"/>
+      <c r="G18" s="42" t="inlineStr"/>
+      <c r="H18" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="40" t="inlineStr">
         <is>
           <t>Aug 2 blog post live</t>
         </is>
       </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr"/>
-      <c r="E19" s="43" t="inlineStr"/>
-      <c r="F19" s="43" t="inlineStr"/>
-      <c r="G19" s="43" t="inlineStr"/>
-      <c r="H19" s="44" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr"/>
+      <c r="E19" s="40" t="inlineStr"/>
+      <c r="F19" s="40" t="inlineStr"/>
+      <c r="G19" s="40" t="inlineStr"/>
+      <c r="H19" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -4867,7 +4946,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="47" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>Q3 Oct–Dec 2026  ·  Theme: Growth &amp; community</t>
         </is>
@@ -4916,156 +4995,156 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="40" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="40" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="40" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr"/>
-      <c r="E23" s="43" t="inlineStr"/>
-      <c r="F23" s="43" t="inlineStr"/>
-      <c r="G23" s="43" t="inlineStr"/>
-      <c r="H23" s="44" t="inlineStr">
+      <c r="D23" s="40" t="inlineStr"/>
+      <c r="E23" s="40" t="inlineStr"/>
+      <c r="F23" s="40" t="inlineStr"/>
+      <c r="G23" s="40" t="inlineStr"/>
+      <c r="H23" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B24" s="45" t="inlineStr">
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C24" s="45" t="inlineStr">
+      <c r="C24" s="42" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="D24" s="45" t="inlineStr"/>
-      <c r="E24" s="45" t="inlineStr"/>
-      <c r="F24" s="45" t="inlineStr"/>
-      <c r="G24" s="45" t="inlineStr"/>
-      <c r="H24" s="44" t="inlineStr">
+      <c r="D24" s="42" t="inlineStr"/>
+      <c r="E24" s="42" t="inlineStr"/>
+      <c r="F24" s="42" t="inlineStr"/>
+      <c r="G24" s="42" t="inlineStr"/>
+      <c r="H24" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>User-filed GitHub issues</t>
         </is>
       </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="40" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr"/>
-      <c r="E25" s="43" t="inlineStr"/>
-      <c r="F25" s="43" t="inlineStr"/>
-      <c r="G25" s="43" t="inlineStr"/>
-      <c r="H25" s="44" t="inlineStr">
+      <c r="D25" s="40" t="inlineStr"/>
+      <c r="E25" s="40" t="inlineStr"/>
+      <c r="F25" s="40" t="inlineStr"/>
+      <c r="G25" s="40" t="inlineStr"/>
+      <c r="H25" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="45" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>v1.6.0 shipped</t>
         </is>
       </c>
-      <c r="B26" s="45" t="inlineStr">
+      <c r="B26" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C26" s="45" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D26" s="45" t="inlineStr"/>
-      <c r="E26" s="45" t="inlineStr"/>
-      <c r="F26" s="45" t="inlineStr"/>
-      <c r="G26" s="45" t="inlineStr"/>
-      <c r="H26" s="44" t="inlineStr">
+      <c r="D26" s="42" t="inlineStr"/>
+      <c r="E26" s="42" t="inlineStr"/>
+      <c r="F26" s="42" t="inlineStr"/>
+      <c r="G26" s="42" t="inlineStr"/>
+      <c r="H26" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="43" t="inlineStr">
+      <c r="A27" s="40" t="inlineStr">
         <is>
           <t>r/python post submitted</t>
         </is>
       </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr"/>
-      <c r="E27" s="43" t="inlineStr"/>
-      <c r="F27" s="43" t="inlineStr"/>
-      <c r="G27" s="43" t="inlineStr"/>
-      <c r="H27" s="44" t="inlineStr">
+      <c r="D27" s="40" t="inlineStr"/>
+      <c r="E27" s="40" t="inlineStr"/>
+      <c r="F27" s="40" t="inlineStr"/>
+      <c r="G27" s="40" t="inlineStr"/>
+      <c r="H27" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>False positive rate (OSS)</t>
         </is>
       </c>
-      <c r="B28" s="45" t="inlineStr">
+      <c r="B28" s="42" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C28" s="45" t="inlineStr">
+      <c r="C28" s="42" t="inlineStr">
         <is>
           <t>&lt; 5%</t>
         </is>
       </c>
-      <c r="D28" s="45" t="inlineStr"/>
-      <c r="E28" s="45" t="inlineStr"/>
-      <c r="F28" s="45" t="inlineStr"/>
-      <c r="G28" s="45" t="inlineStr"/>
-      <c r="H28" s="44" t="inlineStr">
+      <c r="D28" s="42" t="inlineStr"/>
+      <c r="E28" s="42" t="inlineStr"/>
+      <c r="F28" s="42" t="inlineStr"/>
+      <c r="G28" s="42" t="inlineStr"/>
+      <c r="H28" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -5122,156 +5201,156 @@
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="45" t="inlineStr">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>GitHub stars</t>
         </is>
       </c>
-      <c r="B32" s="45" t="inlineStr">
+      <c r="B32" s="42" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C32" s="45" t="inlineStr">
+      <c r="C32" s="42" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D32" s="45" t="inlineStr"/>
-      <c r="E32" s="45" t="inlineStr"/>
-      <c r="F32" s="45" t="inlineStr"/>
-      <c r="G32" s="45" t="inlineStr"/>
-      <c r="H32" s="44" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr"/>
+      <c r="E32" s="42" t="inlineStr"/>
+      <c r="F32" s="42" t="inlineStr"/>
+      <c r="G32" s="42" t="inlineStr"/>
+      <c r="H32" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>PyPI monthly downloads</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="40" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="40" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr"/>
-      <c r="E33" s="43" t="inlineStr"/>
-      <c r="F33" s="43" t="inlineStr"/>
-      <c r="G33" s="43" t="inlineStr"/>
-      <c r="H33" s="44" t="inlineStr">
+      <c r="D33" s="40" t="inlineStr"/>
+      <c r="E33" s="40" t="inlineStr"/>
+      <c r="F33" s="40" t="inlineStr"/>
+      <c r="G33" s="40" t="inlineStr"/>
+      <c r="H33" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="45" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>GitHub Sponsors live</t>
         </is>
       </c>
-      <c r="B34" s="45" t="inlineStr">
+      <c r="B34" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C34" s="45" t="inlineStr">
+      <c r="C34" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D34" s="45" t="inlineStr"/>
-      <c r="E34" s="45" t="inlineStr"/>
-      <c r="F34" s="45" t="inlineStr"/>
-      <c r="G34" s="45" t="inlineStr"/>
-      <c r="H34" s="44" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr"/>
+      <c r="E34" s="42" t="inlineStr"/>
+      <c r="F34" s="42" t="inlineStr"/>
+      <c r="G34" s="42" t="inlineStr"/>
+      <c r="H34" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="A35" s="40" t="inlineStr">
         <is>
           <t>Enterprise enquiries</t>
         </is>
       </c>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="B35" s="40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr"/>
-      <c r="E35" s="43" t="inlineStr"/>
-      <c r="F35" s="43" t="inlineStr"/>
-      <c r="G35" s="43" t="inlineStr"/>
-      <c r="H35" s="44" t="inlineStr">
+      <c r="D35" s="40" t="inlineStr"/>
+      <c r="E35" s="40" t="inlineStr"/>
+      <c r="F35" s="40" t="inlineStr"/>
+      <c r="G35" s="40" t="inlineStr"/>
+      <c r="H35" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="45" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>Year-1 retro published</t>
         </is>
       </c>
-      <c r="B36" s="45" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C36" s="45" t="inlineStr">
+      <c r="C36" s="42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D36" s="45" t="inlineStr"/>
-      <c r="E36" s="45" t="inlineStr"/>
-      <c r="F36" s="45" t="inlineStr"/>
-      <c r="G36" s="45" t="inlineStr"/>
-      <c r="H36" s="44" t="inlineStr">
+      <c r="D36" s="42" t="inlineStr"/>
+      <c r="E36" s="42" t="inlineStr"/>
+      <c r="F36" s="42" t="inlineStr"/>
+      <c r="G36" s="42" t="inlineStr"/>
+      <c r="H36" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="43" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>v2.0 roadmap defined</t>
         </is>
       </c>
-      <c r="B37" s="43" t="inlineStr">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
+      <c r="C37" s="40" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D37" s="43" t="inlineStr"/>
-      <c r="E37" s="43" t="inlineStr"/>
-      <c r="F37" s="43" t="inlineStr"/>
-      <c r="G37" s="43" t="inlineStr"/>
-      <c r="H37" s="44" t="inlineStr">
+      <c r="D37" s="40" t="inlineStr"/>
+      <c r="E37" s="40" t="inlineStr"/>
+      <c r="F37" s="40" t="inlineStr"/>
+      <c r="G37" s="40" t="inlineStr"/>
+      <c r="H37" s="41" t="inlineStr">
         <is>
           <t>R / A / G</t>
         </is>
@@ -5286,35 +5365,35 @@
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="45" t="inlineStr">
         <is>
           <t>• Update the Week columns each Friday. Enter actual numbers, not estimates.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="48" t="inlineStr">
+      <c r="A41" s="45" t="inlineStr">
         <is>
           <t>• RAG = Red (off track, needs action) / Amber (at risk, monitor) / Green (on track).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="48" t="inlineStr">
+      <c r="A42" s="45" t="inlineStr">
         <is>
           <t>• A metric that stays Red for 2+ weeks needs a plan change, not a colour change.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="48" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>• Baseline = value at start of quarter. Target = realistic stretch, based on market data above.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="48" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>• Do not update baselines mid-quarter — that hides regression.</t>
         </is>
@@ -5414,7 +5493,7 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>These 8 weeks determine whether the Show HN lands before or after the August deadline crowd</t>
         </is>
@@ -5453,7 +5532,7 @@
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>Wk 1</t>
         </is>
@@ -5463,7 +5542,7 @@
           <t>Apr 3–9</t>
         </is>
       </c>
-      <c r="C4" s="50" t="inlineStr">
+      <c r="C4" s="47" t="inlineStr">
         <is>
           <t>Pre-launch: repo &amp; landing</t>
         </is>
@@ -5477,7 +5556,7 @@
 □ Verify PyPI page renders description correctly</t>
         </is>
       </c>
-      <c r="E4" s="51" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5489,7 +5568,7 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Wk 2</t>
         </is>
@@ -5499,7 +5578,7 @@
           <t>Apr 10–16</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>Pre-launch: DEV.to research</t>
         </is>
@@ -5513,7 +5592,7 @@
 □ Draft DEV.to article outline</t>
         </is>
       </c>
-      <c r="E5" s="51" t="inlineStr">
+      <c r="E5" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5525,7 +5604,7 @@
       </c>
     </row>
     <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
         <is>
           <t>Wk 3</t>
         </is>
@@ -5535,7 +5614,7 @@
           <t>Apr 17–23</t>
         </is>
       </c>
-      <c r="C6" s="50" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>DEV.to article: write &amp; publish</t>
         </is>
@@ -5549,7 +5628,7 @@
 □ Share on LinkedIn</t>
         </is>
       </c>
-      <c r="E6" s="51" t="inlineStr">
+      <c r="E6" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5561,7 +5640,7 @@
       </c>
     </row>
     <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Wk 4</t>
         </is>
@@ -5571,7 +5650,7 @@
           <t>Apr 24–30</t>
         </is>
       </c>
-      <c r="C7" s="52" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>Show HN prep</t>
         </is>
@@ -5585,7 +5664,7 @@
 □ Block 4 hours in calendar for that day</t>
         </is>
       </c>
-      <c r="E7" s="51" t="inlineStr">
+      <c r="E7" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5597,7 +5676,7 @@
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>Wk 5</t>
         </is>
@@ -5607,7 +5686,7 @@
           <t>May 1–7</t>
         </is>
       </c>
-      <c r="C8" s="50" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Show HN LAUNCH</t>
         </is>
@@ -5621,7 +5700,7 @@
 □ Thank people who try it and report results</t>
         </is>
       </c>
-      <c r="E8" s="51" t="inlineStr">
+      <c r="E8" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5633,7 +5712,7 @@
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>Wk 6</t>
         </is>
@@ -5643,7 +5722,7 @@
           <t>May 8–14</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>Post-HN: follow-up &amp; ecosystem</t>
         </is>
@@ -5657,7 +5736,7 @@
 □ Note which questions came up most — update FAQ</t>
         </is>
       </c>
-      <c r="E9" s="51" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5669,7 +5748,7 @@
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="47" t="inlineStr">
         <is>
           <t>Wk 7</t>
         </is>
@@ -5679,7 +5758,7 @@
           <t>May 15–21</t>
         </is>
       </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="47" t="inlineStr">
         <is>
           <t>Product Hunt prep</t>
         </is>
@@ -5693,7 +5772,7 @@
 □ Schedule for Tuesday launch</t>
         </is>
       </c>
-      <c r="E10" s="51" t="inlineStr">
+      <c r="E10" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>
@@ -5705,7 +5784,7 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>Wk 8</t>
         </is>
@@ -5715,7 +5794,7 @@
           <t>May 22–29</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>EU ecosystem outreach begins</t>
         </is>
@@ -5729,7 +5808,7 @@
 □ Review GitHub stars — assess HN impact honestly</t>
         </is>
       </c>
-      <c r="E11" s="51" t="inlineStr">
+      <c r="E11" s="48" t="inlineStr">
         <is>
           <t>□ Not done</t>
         </is>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -4445,17 +4445,17 @@
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
-          <t>CLI / script</t>
+          <t>Web questionnaire</t>
         </is>
       </c>
       <c r="D16" s="38" t="inlineStr">
         <is>
-          <t>Python script. Scans codebases for EU AI Act compliance. GitHub repo (ARQNXS/eu-ai-act-compliance-checker).</t>
-        </is>
-      </c>
-      <c r="E16" s="35" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>Browser-based compliance questionnaire (arqnxs.github.io). Generates report from answers. Proprietary licence (all rights reserved). No codebase scanning.</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="F16" s="37" t="inlineStr">
@@ -4465,17 +4465,17 @@
       </c>
       <c r="G16" s="38" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>N/A (form-based)</t>
         </is>
       </c>
       <c r="H16" s="38" t="inlineStr">
         <is>
-          <t>Very early stage. No CI/CD integration, no framework mapping, no doc generation.</t>
+          <t>No code scanning, no CLI, no CI/CD. Different approach entirely — self-assessment form, not static analysis.</t>
         </is>
       </c>
       <c r="I16" s="38" t="inlineStr">
         <is>
-          <t>Low — different depth. Found Apr 2026.</t>
+          <t>Very low — different approach. Found Apr 2026.</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4490,7 @@
     <row r="19" ht="90" customHeight="1">
       <c r="A19" s="39" t="inlineStr">
         <is>
-          <t>Regula has the broadest feature set in the open-source CLI space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation, evidence pack, gap scoring, remediation plan). Two direct CLI+CI/CD competitors: Systima Comply (TS-native + tree-sitter, 37+ frameworks, PDF reports, org created 6 Mar 2026, 0 stars) and ARQNXS/eu-ai-act-compliance-checker (Python script, early stage). Regula's advantage over Systima: 33 commands vs scan-only; 36 named pattern groups with dedicated per-language depth; SBOM, inventory, bias eval, and Annex IV docs in one tool. Both tools generate compliance documentation. EuConform leads on OSS mindshare (107 ★ as of Apr 2026 — browser-only, no CLI, no CI/CD).
+          <t>Regula has the broadest feature set in the open-source CLI space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation, evidence pack, gap scoring, remediation plan). One direct CLI+CI/CD competitor: Systima Comply (TS-native + tree-sitter, 37+ frameworks, PDF reports, org created 6 Mar 2026, 0 stars). ARQNXS/eu-ai-act-compliance-checker is a browser questionnaire, not a scanner (proprietary, no code analysis). Regula's advantage over Systima: 33 commands vs scan-only; 36 named pattern groups with dedicated per-language depth; SBOM, inventory, bias eval, and Annex IV docs in one tool. Both tools generate compliance documentation. EuConform leads on OSS mindshare (107 ★ as of Apr 2026 — browser-only, no CLI, no CI/CD).
 The honest risk: EuConform has 107 stars and 4 months head start. Systima is a direct technical competitor with CLI + CI/CD + compliance doc generation. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
 The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
         </is>

--- a/docs/regula_gtm_plan.xlsx
+++ b/docs/regula_gtm_plan.xlsx
@@ -3789,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3813,7 +3813,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>All star counts verified via GitHub API. All claims verified against public sources.</t>
+          <t>Star counts: NOT live-verified — check GitHub directly before using in any pitch. All feature claims verified against public documentation.</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>Regex + AST + tree-sitter. 33 commands, 36 named pattern groups, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, remediation plans.</t>
+          <t>Regex + AST + tree-sitter. 33 commands, 36 named pattern groups, 11 frameworks, 8 languages. Generates Annex IV docs, evidence packs, gap assessment, remediation plans, SBOM, bias eval, model inventory. Free/MIT. Zero deps.</t>
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr">
@@ -3903,25 +3903,26 @@
       </c>
       <c r="H4" s="34" t="inlineStr">
         <is>
-          <t>Most commands (33), most languages (8), deepest pattern coverage (36 named groups); Annex IV + evidence pack + gap scoring + remediation plan in one free tool.</t>
+          <t>Most commands (33), most languages (8), 36 named pattern groups; Annex IV + evidence pack + gap + remediation + SBOM + bias in one free tool.</t>
         </is>
       </c>
       <c r="I4" s="34" t="inlineStr">
         <is>
-          <t>Starting from 0. Late entrant. Systima overlaps on CLI+CI/CD.</t>
+          <t>0 stars, 0 distribution. Every advantage is theoretical until someone uses it.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>EuConform</t>
+          <t>EuConform
+(Hiepler/EuConform)</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>107 ★
-(Apr 2026)</t>
+          <t>~107 ★
+(unverified — check GitHub)</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -3931,7 +3932,7 @@
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>Risk classification (Art.6/7) + bias eval (CrowS-Pairs). Offline-first, no cloud. PDF reports.</t>
+          <t>Risk classification (Art.5–15) + bias eval (CrowS-Pairs). Offline-first, no cloud, no account. PDF reports. Show HN posted 11 Jan 2026. Open source.</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
@@ -3946,29 +3947,31 @@
       </c>
       <c r="G5" s="36" t="inlineStr">
         <is>
-          <t>N/A (form-based)</t>
+          <t>N/A — form-based</t>
         </is>
       </c>
       <c r="H5" s="36" t="inlineStr">
         <is>
-          <t>No CLI, no CI/CD. Cannot integrate into a dev workflow. No codebase scanning.</t>
+          <t>No codebase scanning — classifies by questionnaire, not by reading code. No CI/CD.</t>
         </is>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
-          <t>107 stars as of Apr 2026 — strong first-mover advantage in OSS space</t>
+          <t>OSS first-mover. ~107 stars, 3+ months of mindshare lead. Will be the benchmark comparison on Show HN.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
         <is>
-          <t>Systima Comply</t>
+          <t>Systima Comply
+(@systima/comply)</t>
         </is>
       </c>
       <c r="B6" s="38" t="inlineStr">
         <is>
-          <t>0 ★</t>
+          <t>0 ★
+(unverified — check npm/GitHub)</t>
         </is>
       </c>
       <c r="C6" s="38" t="inlineStr">
@@ -3978,7 +3981,7 @@
       </c>
       <c r="D6" s="38" t="inlineStr">
         <is>
-          <t>npm package + GitHub Action + TypeScript API. Scans codebase for EU AI Act risks. Domain-based severity. PDF reports. Call-chain tracing. 37+ AI frameworks via tree-sitter WASM.</t>
+          <t>npm package + GH Action (systima-ai/comply@v1) + TypeScript API. AST call-chain tracing via TypeScript Compiler API + web-tree-sitter WASM. 37+ AI frameworks detected. Severity adjusted by declared system domain. PDF reports + template compliance docs. Apache 2.0.</t>
         </is>
       </c>
       <c r="E6" s="35" t="inlineStr">
@@ -3993,180 +3996,186 @@
       </c>
       <c r="G6" s="38" t="inlineStr">
         <is>
-          <t>TS-native; also scans Py/Go/Java/Rust via tree-sitter</t>
+          <t>TS-native; also Py/Go/Java/Rust via tree-sitter</t>
         </is>
       </c>
       <c r="H6" s="38" t="inlineStr">
         <is>
-          <t>Regula: 33 commands vs Systima's scan-only; dedicated per-language patterns (36 named groups); evidence pack, gap scoring, and remediation plan. Both generate compliance docs.</t>
+          <t>Regula: 33 commands vs Systima's single scan command; 8 dedicated language parsers; evidence pack, gap scoring, SBOM, bias eval not present in Systima.</t>
         </is>
       </c>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>Direct competitor — CLI + CI/CD + codebase scanning. Org created 6 Mar 2026.</t>
+          <t>MOST DANGEROUS COMPETITOR. CLI + CI/CD + compliance docs + call-chain tracing. Created 6 Mar 2026. Will likely Show HN before Regula does.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>AgentGuard</t>
+          <t>annex4ac
+(PyPI: annex4ac)</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>10 ★</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>Runtime middleware</t>
+          <t>CLI / CI tool</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>3-line Python import. Wraps LLM agents. Runtime policy enforcement, not code scanning.</t>
-        </is>
-      </c>
-      <c r="E7" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr">
-        <is>
-          <t>Yes (SDK)</t>
+          <t>Annex IV-as-Code. Generates and validates EU AI Act Annex IV technical documentation from YAML. Pulls live Annex IV layout from official source. SARIF output for GitHub Code Scanning. One-time paid licence.</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>Yes (GH Action)</t>
         </is>
       </c>
       <c r="G7" s="36" t="inlineStr">
         <is>
-          <t>Python (middleware)</t>
+          <t>Language-agnostic
+(YAML input)</t>
         </is>
       </c>
       <c r="H7" s="36" t="inlineStr">
         <is>
-          <t>Different use case: runtime vs scan-time. Complementary, not competitive.</t>
+          <t>Regula's Annex IV docs are generated from code scan context. annex4ac is a paid doc-only tool — no risk scanning.</t>
         </is>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
-          <t>Could expand to code scanning</t>
+          <t>Directly competes with 'regula docs'. Paid licence is a differentiator in our favour. But it's more specialised for docs teams.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="38" t="inlineStr">
         <is>
-          <t>EU AI Radar</t>
+          <t>mcp-eu-ai-act
+(ark-forge)</t>
         </is>
       </c>
       <c r="B8" s="38" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~2 ★
+(unverified)</t>
         </is>
       </c>
       <c r="C8" s="38" t="inlineStr">
         <is>
-          <t>Static web tool</t>
+          <t>MCP server</t>
         </is>
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>5-question quiz. Maps to risk band. No code scanning.</t>
-        </is>
-      </c>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F8" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Open-source MCP scanner. Detects EU AI Act violations via MCP protocol in Claude/Cursor. Python, scans .py/.js/.ts/.java/.go/.rs/.cpp/.c. Apache 2.0.</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Via MCP</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>Via MCP</t>
         </is>
       </c>
       <c r="G8" s="38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Multi (via file scan)</t>
         </is>
       </c>
       <c r="H8" s="38" t="inlineStr">
         <is>
-          <t>Trivial tool. Different depth entirely.</t>
+          <t>Regula's MCP server covers same use case but with 33 commands behind it. annex4ac generation, gap scoring, evidence pack not present in mcp-eu-ai-act.</t>
         </is>
       </c>
       <c r="I8" s="38" t="inlineStr">
         <is>
-          <t>Very low — different depth</t>
+          <t>Will index in Claude/Cursor tool directories before Regula if we don't submit first.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>mcp-eu-ai-act</t>
+          <t>ARQNXS/eu-ai-act
+-compliance-checker</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>2 ★</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>MCP server</t>
+          <t>Web questionnaire</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>ArkForge MCP scanner. Detects EU AI Act violations via MCP protocol.</t>
-        </is>
-      </c>
-      <c r="E9" s="35" t="inlineStr">
-        <is>
-          <t>Via MCP</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="inlineStr">
-        <is>
-          <t>Via MCP</t>
+          <t>Browser-based self-assessment questionnaire (arqnxs.github.io). Generates compliance report from answers. No codebase scanning. Proprietary licence — all rights reserved.</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" s="36" t="inlineStr">
         <is>
-          <t>MCP-compatible</t>
+          <t>N/A — form-based</t>
         </is>
       </c>
       <c r="H9" s="36" t="inlineStr">
         <is>
-          <t>Very early. Our MCP server is a distribution channel, not a competitor.</t>
+          <t>No code scanning, no CLI, no CI/CD. Different approach entirely.</t>
         </is>
       </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
-          <t>Could gain traction with Claude/Cursor users before us</t>
+          <t>Low. Different job entirely.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="38" t="inlineStr">
         <is>
-          <t>G0 (AgentBouncr)</t>
+          <t>AgentGuard</t>
         </is>
       </c>
       <c r="B10" s="38" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~10 ★
+(unverified)</t>
         </is>
       </c>
       <c r="C10" s="38" t="inlineStr">
         <is>
-          <t>Agent control layer</t>
+          <t>Runtime middleware</t>
         </is>
       </c>
       <c r="D10" s="38" t="inlineStr">
         <is>
-          <t>Scan, test, monitor for AI agents. LangChain/CrewAI/AutoGen/RAG. HMAC audit chains. ConsentGate.</t>
+          <t>3-line Python import. Wraps LLM agents at runtime. Policy enforcement, not static code scanning. Python SDK.</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
@@ -4176,7 +4185,7 @@
       </c>
       <c r="F10" s="35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Yes (SDK)</t>
         </is>
       </c>
       <c r="G10" s="38" t="inlineStr">
@@ -4186,34 +4195,34 @@
       </c>
       <c r="H10" s="38" t="inlineStr">
         <is>
-          <t>Agent-focused vs code-focused. Different buyer.</t>
+          <t>Different job: runtime enforcement vs scan-time risk indication. Complementary.</t>
         </is>
       </c>
       <c r="I10" s="38" t="inlineStr">
         <is>
-          <t>Could expand to code scanning</t>
+          <t>Could expand to static scanning.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>KLA Digital</t>
+          <t>G0 / AgentBouncr</t>
         </is>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>SaaS platform</t>
+          <t>Agent control layer</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>AI governance SaaS. Cross-framework mapping. Pricing on request — no public list prices (Apr 2026).</t>
+          <t>Scan, test, monitor AI agents. LangChain/CrewAI/AutoGen/RAG support. HMAC audit chains. ConsentGate. Python.</t>
         </is>
       </c>
       <c r="E11" s="37" t="inlineStr">
@@ -4221,31 +4230,32 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
-          <t>Platform</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="H11" s="36" t="inlineStr">
         <is>
-          <t>We're free. They target enterprise compliance officers, not developers.</t>
+          <t>Agent-focused, not code-scanner. Different buyer (AI ops vs developer).</t>
         </is>
       </c>
       <c r="I11" s="36" t="inlineStr">
         <is>
-          <t>Credibility: established brand vs unknown</t>
+          <t>Could expand to code scanning.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="38" t="inlineStr">
         <is>
-          <t>EuroComply</t>
+          <t>EuroComply
+(eurocomply.app)</t>
         </is>
       </c>
       <c r="B12" s="38" t="inlineStr">
@@ -4260,7 +4270,7 @@
       </c>
       <c r="D12" s="38" t="inlineStr">
         <is>
-          <t>EU AI Act + NIS2 + GDPR + CRA + Data Act in one platform. Browser-based.</t>
+          <t>EU AI Act + NIS2 + GDPR + CRA + Data Act in one platform. Browser-based. No code scanning.</t>
         </is>
       </c>
       <c r="E12" s="37" t="inlineStr">
@@ -4280,34 +4290,34 @@
       </c>
       <c r="H12" s="38" t="inlineStr">
         <is>
-          <t>Targets same SME audience. Broader regulation coverage. No code scanning.</t>
+          <t>We're free, code-level, zero-dependency. They charge for multi-regulation coverage.</t>
         </is>
       </c>
       <c r="I12" s="38" t="inlineStr">
         <is>
-          <t>Most direct SaaS overlap with Regula's audience</t>
+          <t>Same target audience (SMEs). No code scanning is their gap. Regula should mention this explicitly.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>compl-ai</t>
+          <t>KLA Digital</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>OSS eval framework</t>
+          <t>SaaS platform</t>
         </is>
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>Open-source compliance-centred evaluation for generative AI. compl-ai.org. Research-grade.</t>
+          <t>AI governance SaaS. Cross-framework mapping. No published pricing (Apr 2026).</t>
         </is>
       </c>
       <c r="E13" s="37" t="inlineStr">
@@ -4317,30 +4327,30 @@
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G13" s="36" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="H13" s="36" t="inlineStr">
         <is>
-          <t>Research-focused, not developer-focused. Different use case.</t>
+          <t>Free vs paid. Developer tool vs compliance officer tool.</t>
         </is>
       </c>
       <c r="I13" s="36" t="inlineStr">
         <is>
-          <t>Could grow into developer tool territory</t>
+          <t>Credibility comparison. Established brand.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="38" t="inlineStr">
         <is>
-          <t>Microsoft Agent
-Governance Toolkit</t>
+          <t>OneTrust / Credo AI
+/ Holistic AI</t>
         </is>
       </c>
       <c r="B14" s="38" t="inlineStr">
@@ -4350,158 +4360,66 @@
       </c>
       <c r="C14" s="38" t="inlineStr">
         <is>
-          <t>Enterprise toolkit</t>
+          <t>Enterprise GRC</t>
         </is>
       </c>
       <c r="D14" s="38" t="inlineStr">
         <is>
-          <t>Policy enforcement, zero-trust identity, sandboxing for AI agents. Published 2 Apr 2026.</t>
+          <t>Enterprise AI governance. Credo AI is most EU AI Act-specific per analyst reports. Holistic AI strong in Europe. OneTrust covers GDPR-AI intersection. No published pricing — enterprise contracts.</t>
         </is>
       </c>
       <c r="E14" s="37" t="inlineStr">
         <is>
-          <t>Via SDK</t>
-        </is>
-      </c>
-      <c r="F14" s="35" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="G14" s="38" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Platform</t>
         </is>
       </c>
       <c r="H14" s="38" t="inlineStr">
         <is>
-          <t>Enterprise-only. Microsoft ecosystem. Not code scanning.</t>
+          <t>Entirely different buyer (compliance officers, not developers). We are free. They are not.</t>
         </is>
       </c>
       <c r="I14" s="38" t="inlineStr">
         <is>
-          <t>High credibility. Developer mindshare risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>OneTrust/Credo AI</t>
-        </is>
-      </c>
-      <c r="B15" s="36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>Enterprise GRC</t>
-        </is>
-      </c>
-      <c r="D15" s="36" t="inlineStr">
-        <is>
-          <t>Est. $50K+/year for enterprise contracts. Risk management, documentation, lifecycle.</t>
-        </is>
-      </c>
-      <c r="E15" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G15" s="36" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-      <c r="H15" s="36" t="inlineStr">
-        <is>
-          <t>We're free. Entirely different buyer. Not a real competitor at our stage.</t>
-        </is>
-      </c>
-      <c r="I15" s="36" t="inlineStr">
-        <is>
-          <t>Credibility comparison if enterprise asks why not use them</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
-        <is>
-          <t>ARQNXS/eu-ai-act
--compliance-checker</t>
-        </is>
-      </c>
-      <c r="B16" s="38" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="inlineStr">
-        <is>
-          <t>Web questionnaire</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="inlineStr">
-        <is>
-          <t>Browser-based compliance questionnaire (arqnxs.github.io). Generates report from answers. Proprietary licence (all rights reserved). No codebase scanning.</t>
-        </is>
-      </c>
-      <c r="E16" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F16" s="37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="38" t="inlineStr">
-        <is>
-          <t>N/A (form-based)</t>
-        </is>
-      </c>
-      <c r="H16" s="38" t="inlineStr">
-        <is>
-          <t>No code scanning, no CLI, no CI/CD. Different approach entirely — self-assessment form, not static analysis.</t>
-        </is>
-      </c>
-      <c r="I16" s="38" t="inlineStr">
-        <is>
-          <t>Very low — different approach. Found Apr 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+          <t>Will be the comparison when an enterprise DPO asks 'why not use OneTrust?' Have an answer ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="10" customHeight="1"/>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>HONEST ASSESSMENT</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>Regula has the broadest feature set in the open-source CLI space (33 commands, 8 languages, 11 frameworks, 36 named pattern groups, Annex IV doc generation, evidence pack, gap scoring, remediation plan). One direct CLI+CI/CD competitor: Systima Comply (TS-native + tree-sitter, 37+ frameworks, PDF reports, org created 6 Mar 2026, 0 stars). ARQNXS/eu-ai-act-compliance-checker is a browser questionnaire, not a scanner (proprietary, no code analysis). Regula's advantage over Systima: 33 commands vs scan-only; 36 named pattern groups with dedicated per-language depth; SBOM, inventory, bias eval, and Annex IV docs in one tool. Both tools generate compliance documentation. EuConform leads on OSS mindshare (107 ★ as of Apr 2026 — browser-only, no CLI, no CI/CD).
-The honest risk: EuConform has 107 stars and 4 months head start. Systima is a direct technical competitor with CLI + CI/CD + compliance doc generation. Distribution — not product quality — is the critical path. Every week without a Show HN post or distribution action is a week competitors compound their lead.
-The window is August 2026. After the deadline passes, urgency drops and the market fragments further.</t>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="39" t="inlineStr">
+        <is>
+          <t>HONEST POSITION: Regula has the broadest command surface (33 commands) and the only free tool combining code scanning + Annex IV docs + evidence pack + gap scoring + remediation + SBOM + bias eval in one CLI. That is objectively true. What is also true: 0 stars, 0 distribution, and 0 users.
+DIRECT COMPETITOR: Systima Comply is the most dangerous. CLI + CI/CD + AST call-chain tracing + PDF compliance docs. Created 6 Mar 2026. Their AST call-chain tracing is technically more sophisticated than Regula's regex approach — they trace how AI outputs flow through a program, not just detect patterns. Regula's counter: more commands (33 vs scan-only), more languages (8 with dedicated parsers), more outputs (SBOM, inventory, bias, gap, evidence). Both are free.
+MINDSHARE LEADER: EuConform (~107 stars, Show HN 11 Jan 2026). Browser-based — no CLI, no CI/CD, no codebase scanning. It does something different (questionnaire-based classification) but will appear in every search alongside Regula. Developers will compare them.
+NEW THREAT FOUND: annex4ac (PyPI) is a paid CLI that generates Annex IV docs from CI. It directly overlaps with 'regula docs'. Regula's advantage: free, and generates docs from an actual code scan rather than a YAML template.
+STAR COUNTS ARE UNVERIFIED — do not use these numbers in any public communication without checking GitHub directly first.
+BOTTOM LINE: The product is strong. The distribution is zero. EuConform and Systima are both ahead on visibility. August 2026 is the window. After that deadline, urgency evaporates and late entrants lose.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
